--- a/base_prov/ml/ml_abbott_2026-07-20.xlsx
+++ b/base_prov/ml/ml_abbott_2026-07-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CF1AC4-00C3-4784-BAFB-687012A00ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F3926-84D0-4191-B7D8-30CB9726D2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="150">
   <si>
     <t>fecha</t>
   </si>
@@ -462,12 +462,6 @@
   </si>
   <si>
     <t>https://www.mercadolibre.com.mx/formula-nutricional-polvo-pediasure-ml2-850g-chocolate/p/MLM69624767#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=590f3be8-33a4-4cad-a6eb-76b77124ea07&amp;wid=MLM5336510580&amp;sid=search</t>
-  </si>
-  <si>
-    <t>Fran</t>
-  </si>
-  <si>
-    <t>Bren</t>
   </si>
   <si>
     <t>ASI Proveedora</t>
@@ -869,10 +863,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -919,9 +913,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -965,13 +959,10 @@
       <c r="O2" t="s">
         <v>9</v>
       </c>
-      <c r="P2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1015,13 +1006,10 @@
       <c r="O3" t="s">
         <v>9</v>
       </c>
-      <c r="P3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -1065,13 +1053,10 @@
       <c r="O4" t="s">
         <v>9</v>
       </c>
-      <c r="P4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1115,13 +1100,10 @@
       <c r="O5" t="s">
         <v>9</v>
       </c>
-      <c r="P5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1160,18 +1142,15 @@
         <v>895</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O6" t="s">
         <v>9</v>
       </c>
-      <c r="P6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1215,13 +1194,10 @@
       <c r="O7" t="s">
         <v>9</v>
       </c>
-      <c r="P7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1265,13 +1241,10 @@
       <c r="O8" t="s">
         <v>9</v>
       </c>
-      <c r="P8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1315,13 +1288,10 @@
       <c r="O9" t="s">
         <v>9</v>
       </c>
-      <c r="P9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1365,13 +1335,10 @@
       <c r="O10" t="s">
         <v>9</v>
       </c>
-      <c r="P10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1415,13 +1382,10 @@
       <c r="O11" t="s">
         <v>9</v>
       </c>
-      <c r="P11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -1465,13 +1429,10 @@
       <c r="O12" t="s">
         <v>9</v>
       </c>
-      <c r="P12" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1515,13 +1476,10 @@
       <c r="O13" t="s">
         <v>9</v>
       </c>
-      <c r="P13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1565,13 +1523,10 @@
       <c r="O14" t="s">
         <v>11</v>
       </c>
-      <c r="P14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1615,13 +1570,10 @@
       <c r="O15" t="s">
         <v>11</v>
       </c>
-      <c r="P15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1665,13 +1617,10 @@
       <c r="O16" t="s">
         <v>11</v>
       </c>
-      <c r="P16" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -1715,13 +1664,10 @@
       <c r="O17" t="s">
         <v>9</v>
       </c>
-      <c r="P17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1765,13 +1711,10 @@
       <c r="O18" t="s">
         <v>9</v>
       </c>
-      <c r="P18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -1815,13 +1758,10 @@
       <c r="O19" t="s">
         <v>11</v>
       </c>
-      <c r="P19" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -1865,13 +1805,10 @@
       <c r="O20" t="s">
         <v>9</v>
       </c>
-      <c r="P20" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -1915,13 +1852,10 @@
       <c r="O21" t="s">
         <v>9</v>
       </c>
-      <c r="P21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1965,13 +1899,10 @@
       <c r="O22" t="s">
         <v>9</v>
       </c>
-      <c r="P22" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -2015,13 +1946,10 @@
       <c r="O23" t="s">
         <v>9</v>
       </c>
-      <c r="P23" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -2065,13 +1993,10 @@
       <c r="O24" t="s">
         <v>9</v>
       </c>
-      <c r="P24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -2115,13 +2040,10 @@
       <c r="O25" t="s">
         <v>9</v>
       </c>
-      <c r="P25" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -2165,13 +2087,10 @@
       <c r="O26" t="s">
         <v>9</v>
       </c>
-      <c r="P26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2215,13 +2134,10 @@
       <c r="O27" t="s">
         <v>9</v>
       </c>
-      <c r="P27" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2265,13 +2181,10 @@
       <c r="O28" t="s">
         <v>9</v>
       </c>
-      <c r="P28" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -2315,13 +2228,10 @@
       <c r="O29" t="s">
         <v>9</v>
       </c>
-      <c r="P29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -2365,13 +2275,10 @@
       <c r="O30" t="s">
         <v>9</v>
       </c>
-      <c r="P30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -2415,13 +2322,10 @@
       <c r="O31" t="s">
         <v>11</v>
       </c>
-      <c r="P31" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -2465,13 +2369,10 @@
       <c r="O32" t="s">
         <v>11</v>
       </c>
-      <c r="P32" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -2515,13 +2416,10 @@
       <c r="O33" t="s">
         <v>11</v>
       </c>
-      <c r="P33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -2565,13 +2463,10 @@
       <c r="O34" t="s">
         <v>11</v>
       </c>
-      <c r="P34" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -2615,13 +2510,10 @@
       <c r="O35" t="s">
         <v>11</v>
       </c>
-      <c r="P35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -2665,13 +2557,10 @@
       <c r="O36" t="s">
         <v>11</v>
       </c>
-      <c r="P36" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -2715,13 +2604,10 @@
       <c r="O37" t="s">
         <v>11</v>
       </c>
-      <c r="P37" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -2765,13 +2651,10 @@
       <c r="O38" t="s">
         <v>11</v>
       </c>
-      <c r="P38" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -2815,13 +2698,10 @@
       <c r="O39" t="s">
         <v>11</v>
       </c>
-      <c r="P39" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -2865,13 +2745,10 @@
       <c r="O40" t="s">
         <v>11</v>
       </c>
-      <c r="P40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -2910,18 +2787,15 @@
         <v>141</v>
       </c>
       <c r="N41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O41" t="s">
         <v>9</v>
       </c>
-      <c r="P41" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -2960,18 +2834,15 @@
         <v>141</v>
       </c>
       <c r="N42" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O42" t="s">
         <v>9</v>
       </c>
-      <c r="P42" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -3015,13 +2886,10 @@
       <c r="O43" t="s">
         <v>11</v>
       </c>
-      <c r="P43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -3060,18 +2928,15 @@
         <v>141</v>
       </c>
       <c r="N44" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O44" t="s">
         <v>9</v>
       </c>
-      <c r="P44" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -3115,13 +2980,10 @@
       <c r="O45" t="s">
         <v>11</v>
       </c>
-      <c r="P45" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3160,18 +3022,15 @@
         <v>141</v>
       </c>
       <c r="N46" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O46" t="s">
         <v>9</v>
       </c>
-      <c r="P46" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -3215,13 +3074,10 @@
       <c r="O47" t="s">
         <v>11</v>
       </c>
-      <c r="P47" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -3265,13 +3121,10 @@
       <c r="O48" t="s">
         <v>11</v>
       </c>
-      <c r="P48" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -3315,13 +3168,10 @@
       <c r="O49" t="s">
         <v>11</v>
       </c>
-      <c r="P49" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -3365,13 +3215,10 @@
       <c r="O50" t="s">
         <v>11</v>
       </c>
-      <c r="P50" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -3415,13 +3262,10 @@
       <c r="O51" t="s">
         <v>11</v>
       </c>
-      <c r="P51" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -3465,13 +3309,10 @@
       <c r="O52" t="s">
         <v>11</v>
       </c>
-      <c r="P52" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -3515,13 +3356,10 @@
       <c r="O53" t="s">
         <v>11</v>
       </c>
-      <c r="P53" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -3565,13 +3403,10 @@
       <c r="O54" t="s">
         <v>11</v>
       </c>
-      <c r="P54" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -3615,13 +3450,10 @@
       <c r="O55" t="s">
         <v>11</v>
       </c>
-      <c r="P55" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -3665,13 +3497,10 @@
       <c r="O56" t="s">
         <v>11</v>
       </c>
-      <c r="P56" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -3715,13 +3544,10 @@
       <c r="O57" t="s">
         <v>11</v>
       </c>
-      <c r="P57" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -3760,18 +3586,15 @@
         <v>923</v>
       </c>
       <c r="N58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O58" t="s">
         <v>9</v>
       </c>
-      <c r="P58" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3815,13 +3638,10 @@
       <c r="O59" t="s">
         <v>11</v>
       </c>
-      <c r="P59" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3865,13 +3685,10 @@
       <c r="O60" t="s">
         <v>11</v>
       </c>
-      <c r="P60" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3915,13 +3732,10 @@
       <c r="O61" t="s">
         <v>11</v>
       </c>
-      <c r="P61" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3965,13 +3779,10 @@
       <c r="O62" t="s">
         <v>11</v>
       </c>
-      <c r="P62" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4016,9 +3827,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -4065,7 +3876,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -4112,7 +3923,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -4159,7 +3970,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -4206,7 +4017,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -4253,7 +4064,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -4300,7 +4111,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -4347,7 +4158,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -4394,7 +4205,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -4441,7 +4252,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -4488,7 +4299,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -4535,7 +4346,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -4582,7 +4393,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -4597,7 +4408,7 @@
         <v>123</v>
       </c>
       <c r="F76" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G76">
         <v>5000</v>
@@ -4629,7 +4440,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -4676,7 +4487,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -4723,7 +4534,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -4770,7 +4581,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
